--- a/media/Levels/kakeraMapLevel12.xlsx
+++ b/media/Levels/kakeraMapLevel12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9406336-675B-439E-B52C-9A2375D89CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0742933F-128C-4CE7-9572-3B95DE6AC2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="576" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -33,6 +33,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27544,7 +27553,7 @@
       <c r="CB60">
         <v>0</v>
       </c>
-      <c r="CC60">
+      <c r="CC60" t="s">
         <v>0</v>
       </c>
       <c r="CD60">
@@ -39800,28 +39809,28 @@
         <v>0</v>
       </c>
       <c r="BS87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA87">
         <v>0</v>
@@ -40255,28 +40264,28 @@
         <v>0</v>
       </c>
       <c r="BS88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA88">
         <v>0</v>
@@ -40710,28 +40719,28 @@
         <v>0</v>
       </c>
       <c r="BS89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA89">
         <v>0</v>
@@ -41165,28 +41174,28 @@
         <v>0</v>
       </c>
       <c r="BS90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA90">
         <v>0</v>
@@ -41620,28 +41629,28 @@
         <v>0</v>
       </c>
       <c r="BS91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA91">
         <v>0</v>
@@ -42075,28 +42084,28 @@
         <v>0</v>
       </c>
       <c r="BS92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA92">
         <v>0</v>
@@ -42530,28 +42539,28 @@
         <v>0</v>
       </c>
       <c r="BS93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA93">
         <v>0</v>
@@ -42985,28 +42994,28 @@
         <v>0</v>
       </c>
       <c r="BS94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA94">
         <v>0</v>
@@ -43440,28 +43449,28 @@
         <v>0</v>
       </c>
       <c r="BS95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA95">
         <v>0</v>
